--- a/Excel/ExclusiveDevourConfig.xlsx
+++ b/Excel/ExclusiveDevourConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -105,6 +110,18 @@
   </si>
   <si>
     <t>1350,40000</t>
+  </si>
+  <si>
+    <t>4063,4010</t>
+  </si>
+  <si>
+    <t>150,15000</t>
+  </si>
+  <si>
+    <t>450,30000</t>
+  </si>
+  <si>
+    <t>1350,60000</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1117,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I21"/>
+  <dimension ref="C3:I25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="5" width="9" style="1"/>
@@ -1386,7 +1403,7 @@
         <v>23</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>15</v>
@@ -1409,7 +1426,7 @@
         <v>24</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>15</v>
@@ -1432,9 +1449,78 @@
         <v>25</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I21" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:9">
+      <c r="C23" s="1">
+        <v>34</v>
+      </c>
+      <c r="D23" s="1">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:9">
+      <c r="C24" s="1">
+        <v>35</v>
+      </c>
+      <c r="D24" s="1">
+        <v>5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:9">
+      <c r="C25" s="1">
+        <v>36</v>
+      </c>
+      <c r="D25" s="1">
+        <v>5</v>
+      </c>
+      <c r="E25" s="1">
+        <v>3</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>15</v>
       </c>
     </row>
